--- a/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer fruta</t>
+          <t>Menores según la edad en meses en la que empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,62</t>
+          <t>4,66; 5,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,19</t>
+          <t>5,31; 7,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,59</t>
+          <t>5,27; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,42</t>
+          <t>5,23; 7,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,88</t>
+          <t>5,19; 6,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,92</t>
+          <t>5,24; 13,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,75</t>
+          <t>5,17; 6,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,81</t>
+          <t>5,46; 6,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,31</t>
+          <t>5,65; 11,06</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,52</t>
+          <t>4,86; 5,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 5,73</t>
+          <t>5,25; 5,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,44</t>
+          <t>5,54; 6,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,69</t>
+          <t>4,92; 5,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -812,22 +812,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,22</t>
+          <t>5,35; 6,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,45</t>
+          <t>4,98; 5,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 5,92</t>
+          <t>5,42; 5,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 6,15</t>
+          <t>5,55; 6,19</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,5</t>
+          <t>4,54; 5,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,31</t>
+          <t>5,27; 9,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,42</t>
+          <t>4,86; 5,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,05</t>
+          <t>5,01; 6,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,89</t>
+          <t>5,12; 5,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,37</t>
+          <t>4,78; 5,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,22</t>
+          <t>5,3; 7,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,11</t>
+          <t>5,4; 6,13</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,4</t>
+          <t>4,89; 5,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,5</t>
+          <t>5,42; 6,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,34</t>
+          <t>5,64; 6,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,05</t>
+          <t>5,42; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,12</t>
+          <t>5,42; 6,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,4</t>
+          <t>5,02; 5,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,15</t>
+          <t>5,51; 6,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 6,12</t>
+          <t>5,61; 6,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 5,65</t>
+          <t>4,66; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 7,55</t>
+          <t>5,38; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,64</t>
+          <t>5,21; 9,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,49</t>
+          <t>5,14; 7,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,79</t>
+          <t>5,22; 6,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,85</t>
+          <t>5,36; 15,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,62</t>
+          <t>5,19; 6,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,69</t>
+          <t>5,47; 6,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,06</t>
+          <t>5,73; 10,42</t>
         </is>
       </c>
     </row>
@@ -787,37 +787,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,51</t>
+          <t>4,87; 5,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 5,76</t>
+          <t>5,26; 5,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,38</t>
+          <t>5,57; 6,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,66</t>
+          <t>4,9; 5,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,32</t>
+          <t>5,42; 6,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,19</t>
+          <t>5,33; 6,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 5,47</t>
+          <t>4,96; 5,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,19</t>
+          <t>5,52; 6,17</t>
         </is>
       </c>
     </row>
@@ -897,32 +897,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,51</t>
+          <t>4,49; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,07</t>
+          <t>5,31; 9,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 6,69</t>
+          <t>5,5; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,45</t>
+          <t>4,85; 5,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,0</t>
+          <t>5,01; 6,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 5,84</t>
+          <t>5,11; 5,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,25</t>
+          <t>5,3; 7,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,13</t>
+          <t>5,4; 6,15</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,4</t>
+          <t>4,88; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,55</t>
+          <t>5,43; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,37</t>
+          <t>5,63; 6,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,1</t>
+          <t>5,43; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,12</t>
+          <t>5,45; 6,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,39</t>
+          <t>5,03; 5,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,11</t>
+          <t>5,51; 6,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 6,09</t>
+          <t>5,62; 6,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 5,61</t>
+          <t>5,23; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,47</t>
+          <t>5,27; 6,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,61</t>
+          <t>5,23; 13,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,39</t>
+          <t>4,68; 5,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,91</t>
+          <t>5,32; 7,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,01</t>
+          <t>5,2; 9,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,7</t>
+          <t>5,21; 6,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 6,73</t>
+          <t>5,49; 6,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,42</t>
+          <t>5,62; 10,31</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,82</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,74</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,47</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,51</t>
+          <t>4,93; 5,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 5,76</t>
+          <t>5,46; 6,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 6,43</t>
+          <t>5,33; 6,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,66</t>
+          <t>4,89; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,29</t>
+          <t>5,23; 5,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,24</t>
+          <t>5,54; 6,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,46</t>
+          <t>4,95; 5,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 5,92</t>
+          <t>5,41; 5,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,17</t>
+          <t>5,53; 6,15</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,47</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,04</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,48</t>
+          <t>4,84; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 9,52</t>
+          <t>5,02; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,84</t>
+          <t>5,1; 5,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,45</t>
+          <t>4,49; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,01</t>
+          <t>5,26; 9,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,84</t>
+          <t>5,41; 6,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,36</t>
+          <t>4,79; 5,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,16</t>
+          <t>5,32; 7,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,15</t>
+          <t>5,36; 6,11</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,71</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,95</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,71</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,36</t>
+          <t>5,06; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,69</t>
+          <t>5,44; 6,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,35</t>
+          <t>5,4; 6,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,59</t>
+          <t>4,86; 5,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,1</t>
+          <t>5,42; 6,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,09</t>
+          <t>5,64; 6,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,41</t>
+          <t>5,03; 5,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,12</t>
+          <t>5,51; 6,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,13</t>
+          <t>5,6; 6,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,14</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.115608327358597</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.915344618573425</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.92336910680763</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.196304662882375</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.959482227044464</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.54634045056972</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>5.750854111634175</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>5.939351150917612</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.144294115260831</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 7,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,27; 6,88</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 13,92</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,68; 5,62</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5,32; 7,19</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,2; 9,59</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,21; 6,75</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5,49; 6,81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,62; 10,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.228067094025691</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.272382533566771</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.225613425033401</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.676612245897346</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>5.32346780313991</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>5.204010893199646</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>5.213839562341477</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>5.485543119026056</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.617391942995507</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.416933182667279</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.882881440561759</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.92032436847454</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.618718148579615</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7.186910242169506</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9.594230840152891</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>6.748045923267787</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.806459557572496</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>10.30964959270753</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,91</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,93; 5,69</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 6,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5,33; 6,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,89; 5,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 5,73</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,54; 6,44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,95; 5,45</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 5,92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,53; 6,15</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.221826092551373</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.816701469590703</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.739010490044445</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.133843475376103</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.466731709233934</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.909207402117114</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.179477638525201</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.64124839965038</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.82585230319111</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,95</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.926206911325985</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5.463889823344428</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.328132814319989</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.893712699609163</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5.230032039735503</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>5.540117728590029</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.953147222070009</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>5.406966655688533</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.534995791068211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,84; 5,42</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5,02; 6,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 5,89</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 5,5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,26; 9,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 6,69</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,79; 5,37</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5,32; 7,22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5,36; 6,11</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.690207891683936</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.318417359210639</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.215609368285003</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.518660208633149</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.733939856904819</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6.442359709905535</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.445801532725312</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.917232723086459</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6.153435165708538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,71</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,95</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.125447174353633</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.397875989916603</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.468547836891343</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.037963175029126</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.361803609538622</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5.947836221361</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.081670142030167</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>5.844617694757817</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.688897045122775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,06; 5,59</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,44; 6,05</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,4; 6,12</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 5,4</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,42; 6,5</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,64; 6,34</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 5,4</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5,51; 6,15</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,6; 6,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4.837158928435369</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>5.018622517550114</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.09504674388013</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4.489034093741165</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>5.258887105650632</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.410850719821276</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.792454917633032</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>5.323034883257491</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.358260284269966</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.423709423518652</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.049389816468716</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.892084412587225</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.496114174046244</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.314445512270758</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.689052312412663</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.365005081081085</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>7.221584633800286</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.106974364312356</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.298324528551575</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.710595214729491</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.729992355479321</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.106738958104593</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5.73521642629132</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.95198247770825</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.206592753018617</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>5.722800920856931</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5.840283022859533</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5.059376369386281</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5.441791039025824</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.396243719132714</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.864914916957367</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>5.417174316414541</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.642872783485523</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>5.032463327869095</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>5.510421456459165</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.601660424482842</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.585080628370969</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.051160146706757</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.116072155068721</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.395361279422414</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>6.504168994692128</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>6.342453230769372</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5.396416829787495</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>6.147643096744976</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6.123516646260975</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
